--- a/entertainment_forms/011_theater_performance_attendance_form--entertainment_forms.xlsx
+++ b/entertainment_forms/011_theater_performance_attendance_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>confirm_attendance</t>
+          <t>confirm_attendance_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Confirm Attendance</t>
+          <t>Confirm Attendance 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>confirm_phone</t>
+          <t>confirm_phone_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Confirm Phone</t>
+          <t>Confirm Phone 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>confirm_email</t>
+          <t>confirm_email_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Confirm Email</t>
+          <t>Confirm Email 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>confirm_ticket_info</t>
+          <t>confirm_ticket_info_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Confirm Ticket Info</t>
+          <t>Confirm Ticket Info 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>confirm_seat_selection</t>
+          <t>confirm_seat_selection_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Confirm Seat Selection</t>
+          <t>Confirm Seat Selection 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>confirm_payment_info</t>
+          <t>confirm_payment_info_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Confirm Payment Info</t>
+          <t>Confirm Payment Info 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>confirm_attendance_choices</t>
+          <t>confirm_attendance_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>confirm_attendance_choices</t>
+          <t>confirm_attendance_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>confirm_phone_choices</t>
+          <t>confirm_phone_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>confirm_phone_choices</t>
+          <t>confirm_phone_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>confirm_email_choices</t>
+          <t>confirm_email_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>confirm_email_choices</t>
+          <t>confirm_email_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>confirm_ticket_info_choices</t>
+          <t>confirm_ticket_info_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>confirm_ticket_info_choices</t>
+          <t>confirm_ticket_info_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>confirm_seat_selection_choices</t>
+          <t>confirm_seat_selection_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>confirm_seat_selection_choices</t>
+          <t>confirm_seat_selection_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>confirm_payment_info_choices</t>
+          <t>confirm_payment_info_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>confirm_payment_info_choices</t>
+          <t>confirm_payment_info_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
